--- a/data/trans_camb/P1435-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1435-Estudios-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,07</t>
+          <t>-2,14</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,07</t>
+          <t>-2,14</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,66; -1,27</t>
+          <t>-3,66; -1,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; -2,16</t>
+          <t>-4,19; -2,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,3; -0,82</t>
+          <t>-3,45; -0,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,66; -1,27</t>
+          <t>-3,66; -1,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; -2,16</t>
+          <t>-4,19; -2,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,3; -0,82</t>
+          <t>-3,45; -0,94</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-58,85%</t>
+          <t>-60,85%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-58,85%</t>
+          <t>-60,85%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-83,0; -43,46</t>
+          <t>-82,74; -42,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-97,16; -71,01</t>
+          <t>-97,2; -73,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-79,24; -26,04</t>
+          <t>-78,96; -26,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-83,0; -43,46</t>
+          <t>-82,74; -42,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-97,16; -71,01</t>
+          <t>-97,2; -73,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,24; -26,04</t>
+          <t>-78,96; -26,58</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,74</t>
+          <t>-3,57</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,74</t>
+          <t>-3,57</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,65; -3,2</t>
+          <t>-6,76; -3,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,67; -6,31</t>
+          <t>-9,71; -6,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 8,77</t>
+          <t>-5,46; -1,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,65; -3,2</t>
+          <t>-6,76; -3,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,67; -6,31</t>
+          <t>-9,71; -6,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 8,77</t>
+          <t>-5,46; -1,8</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-17,0%</t>
+          <t>-34,87%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-17,0%</t>
+          <t>-34,87%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-59,1; -34,25</t>
+          <t>-60,85; -34,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-84,93; -70,41</t>
+          <t>-85,11; -70,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,68; 91,38</t>
+          <t>-47,66; -18,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-59,1; -34,25</t>
+          <t>-60,85; -34,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,93; -70,41</t>
+          <t>-85,11; -70,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,68; 91,38</t>
+          <t>-47,66; -18,93</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,72</t>
+          <t>-0,78</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,72</t>
+          <t>-0,78</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; -0,74</t>
+          <t>-8,42; -0,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,77; -3,98</t>
+          <t>-10,51; -4,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 2,92</t>
+          <t>-4,5; 2,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; -0,74</t>
+          <t>-8,42; -0,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,77; -3,98</t>
+          <t>-10,51; -4,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 2,92</t>
+          <t>-4,5; 2,8</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-6,7%</t>
+          <t>-7,18%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-6,7%</t>
+          <t>-7,18%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-62,3; -6,18</t>
+          <t>-63,95; -8,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-81,79; -44,53</t>
+          <t>-81,35; -45,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 33,91</t>
+          <t>-33,28; 31,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-62,3; -6,18</t>
+          <t>-63,95; -8,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-81,79; -44,53</t>
+          <t>-81,35; -45,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 33,91</t>
+          <t>-33,28; 31,66</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>-1,54</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>-1,54</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,95; -2,73</t>
+          <t>-5,02; -2,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,82; -4,79</t>
+          <t>-6,91; -4,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 5,84</t>
+          <t>-2,78; -0,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,95; -2,73</t>
+          <t>-5,02; -2,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,82; -4,79</t>
+          <t>-6,91; -4,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 5,84</t>
+          <t>-2,78; -0,29</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-4,86%</t>
+          <t>-20,0%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-4,86%</t>
+          <t>-20,0%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-59,85; -38,54</t>
+          <t>-59,68; -38,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-80,97; -68,0</t>
+          <t>-81,43; -68,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 79,09</t>
+          <t>-33,28; -3,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-59,85; -38,54</t>
+          <t>-59,68; -38,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-80,97; -68,0</t>
+          <t>-81,43; -68,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 79,09</t>
+          <t>-33,28; -3,7</t>
         </is>
       </c>
     </row>
